--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58790</v>
+        <v>58845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58845</v>
+        <v>58858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -968,11 +968,7 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58860</v>
+        <v>58870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58872</v>
+        <v>58876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 221-2023 artfynd.xlsx
+++ b/artfynd/S 221-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>120912175</v>
       </c>
       <c r="B4" t="n">
-        <v>58876</v>
+        <v>58879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
